--- a/data/sample/sales_raw_data.xlsx
+++ b/data/sample/sales_raw_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajar\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajar\OneDrive\Desktop\Supply-Chain-Analytics-rajarshi\data\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDCF773D-B59B-470D-9AD8-56879B8DAEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0411F75-8639-406D-BECD-3FD962FABB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17532" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18719" uniqueCount="405">
   <si>
     <t>order_id</t>
   </si>
@@ -1270,11 +1270,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1577,55 +1574,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L2191"/>
+  <dimension ref="A1:L2341"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="4" width="14.109375" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="12.88671875" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="13.21875" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -84846,6 +84832,5658 @@
         <v>18</v>
       </c>
       <c r="L2191" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2192">
+        <v>995</v>
+      </c>
+      <c r="B2192" t="s">
+        <v>205</v>
+      </c>
+      <c r="C2192" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2192" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2192" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2192" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2192" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2192">
+        <v>23</v>
+      </c>
+      <c r="I2192">
+        <v>800</v>
+      </c>
+      <c r="J2192">
+        <v>18400</v>
+      </c>
+      <c r="K2192" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2192" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2193">
+        <v>-1386</v>
+      </c>
+      <c r="B2193" t="s">
+        <v>270</v>
+      </c>
+      <c r="C2193" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2193" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2193" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2193" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2193" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2193">
+        <v>46</v>
+      </c>
+      <c r="I2193">
+        <v>3500</v>
+      </c>
+      <c r="J2193">
+        <v>52500</v>
+      </c>
+      <c r="K2193" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2193" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2194">
+        <v>350</v>
+      </c>
+      <c r="B2194" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2194" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2194" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2194" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2194" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2194" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2194">
+        <v>36</v>
+      </c>
+      <c r="I2194">
+        <v>30000</v>
+      </c>
+      <c r="J2194">
+        <v>1080000</v>
+      </c>
+      <c r="K2194" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2194" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2195">
+        <v>329</v>
+      </c>
+      <c r="B2195" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2195" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2195" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2195" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2195" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2195" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2195">
+        <v>32</v>
+      </c>
+      <c r="I2195">
+        <v>3500</v>
+      </c>
+      <c r="J2195">
+        <v>227490</v>
+      </c>
+      <c r="K2195" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2195" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2196">
+        <v>-559</v>
+      </c>
+      <c r="B2196" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2196" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2196" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2196" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2196" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2196" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2196">
+        <v>23</v>
+      </c>
+      <c r="I2196">
+        <v>60000</v>
+      </c>
+      <c r="J2196">
+        <v>1380000</v>
+      </c>
+      <c r="K2196" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2196" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2197">
+        <v>636</v>
+      </c>
+      <c r="B2197" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2197" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2197" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2197" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2197" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2197" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2197">
+        <v>-6</v>
+      </c>
+      <c r="I2197">
+        <v>3500</v>
+      </c>
+      <c r="J2197">
+        <v>59451</v>
+      </c>
+      <c r="K2197" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2197" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2198">
+        <v>803</v>
+      </c>
+      <c r="B2198" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2198" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2198" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2198" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2198" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2198" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2198">
+        <v>37</v>
+      </c>
+      <c r="I2198">
+        <v>834</v>
+      </c>
+      <c r="J2198">
+        <v>29600</v>
+      </c>
+      <c r="K2198" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2198" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2199">
+        <v>75</v>
+      </c>
+      <c r="B2199" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2199" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2199" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2199" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2199" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2199">
+        <v>17</v>
+      </c>
+      <c r="I2199">
+        <v>76</v>
+      </c>
+      <c r="J2199">
+        <v>1020</v>
+      </c>
+      <c r="K2199" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2199" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2200">
+        <v>1952</v>
+      </c>
+      <c r="B2200" t="s">
+        <v>365</v>
+      </c>
+      <c r="C2200" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2200" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2200" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2200" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2200" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2200">
+        <v>67</v>
+      </c>
+      <c r="I2200">
+        <v>29963</v>
+      </c>
+      <c r="J2200">
+        <v>2010000</v>
+      </c>
+      <c r="K2200" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2200" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2201">
+        <v>897</v>
+      </c>
+      <c r="B2201" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2201" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2201" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2201" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2201" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2201" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2201">
+        <v>39</v>
+      </c>
+      <c r="I2201">
+        <v>3500</v>
+      </c>
+      <c r="J2201">
+        <v>98011</v>
+      </c>
+      <c r="K2201" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2201" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2202">
+        <v>1526</v>
+      </c>
+      <c r="B2202" t="s">
+        <v>294</v>
+      </c>
+      <c r="C2202" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2202" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2202" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2202" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2202" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2202">
+        <v>32</v>
+      </c>
+      <c r="I2202">
+        <v>30012</v>
+      </c>
+      <c r="J2202">
+        <v>960000</v>
+      </c>
+      <c r="K2202" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2202" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2203">
+        <v>2060</v>
+      </c>
+      <c r="B2203" t="s">
+        <v>383</v>
+      </c>
+      <c r="C2203" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2203" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2203" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2203" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2203">
+        <v>62</v>
+      </c>
+      <c r="I2203">
+        <v>30000</v>
+      </c>
+      <c r="J2203">
+        <v>839978</v>
+      </c>
+      <c r="K2203" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2203" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2204">
+        <v>382</v>
+      </c>
+      <c r="B2204" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2204" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2204" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2204" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2204" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2204" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2204">
+        <v>-10</v>
+      </c>
+      <c r="I2204">
+        <v>60</v>
+      </c>
+      <c r="J2204">
+        <v>2040</v>
+      </c>
+      <c r="K2204" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2204" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2205">
+        <v>1932</v>
+      </c>
+      <c r="B2205" t="s">
+        <v>361</v>
+      </c>
+      <c r="C2205" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2205" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2205" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2205" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2205" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2205">
+        <v>32</v>
+      </c>
+      <c r="I2205">
+        <v>3500</v>
+      </c>
+      <c r="J2205">
+        <v>112000</v>
+      </c>
+      <c r="K2205" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2205" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2206">
+        <v>435</v>
+      </c>
+      <c r="B2206" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2206" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2206" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2206" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2206" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2206" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2206">
+        <v>46</v>
+      </c>
+      <c r="I2206">
+        <v>5000</v>
+      </c>
+      <c r="J2206">
+        <v>130020</v>
+      </c>
+      <c r="K2206" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2206" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2207">
+        <v>633</v>
+      </c>
+      <c r="B2207" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2207" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2207" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2207" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2207" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2207" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2207">
+        <v>23</v>
+      </c>
+      <c r="I2207">
+        <v>5000</v>
+      </c>
+      <c r="J2207">
+        <v>115000</v>
+      </c>
+      <c r="K2207" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2207" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2208">
+        <v>-1335</v>
+      </c>
+      <c r="B2208" t="s">
+        <v>260</v>
+      </c>
+      <c r="C2208" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2208" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2208" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2208" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2208" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2208">
+        <v>31</v>
+      </c>
+      <c r="I2208">
+        <v>30015</v>
+      </c>
+      <c r="J2208">
+        <v>930000</v>
+      </c>
+      <c r="K2208" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2208" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2209">
+        <v>1649</v>
+      </c>
+      <c r="B2209" t="s">
+        <v>309</v>
+      </c>
+      <c r="C2209" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2209" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2209" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2209" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2209" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2209">
+        <v>12</v>
+      </c>
+      <c r="I2209">
+        <v>3500</v>
+      </c>
+      <c r="J2209">
+        <v>42000</v>
+      </c>
+      <c r="K2209" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2209" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2210">
+        <v>530</v>
+      </c>
+      <c r="B2210" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2210" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2210" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2210" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2210" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2210" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2210">
+        <v>32</v>
+      </c>
+      <c r="I2210">
+        <v>30000</v>
+      </c>
+      <c r="J2210">
+        <v>960016</v>
+      </c>
+      <c r="K2210" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2210" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2211">
+        <v>1610</v>
+      </c>
+      <c r="B2211" t="s">
+        <v>308</v>
+      </c>
+      <c r="C2211" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2211" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2211" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2211" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2211" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2211">
+        <v>48</v>
+      </c>
+      <c r="I2211">
+        <v>30000</v>
+      </c>
+      <c r="J2211">
+        <v>1440039</v>
+      </c>
+      <c r="K2211" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2211" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2212">
+        <v>618</v>
+      </c>
+      <c r="B2212" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2212" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2212" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2212" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2212" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2212" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2212">
+        <v>25</v>
+      </c>
+      <c r="I2212">
+        <v>3534</v>
+      </c>
+      <c r="J2212">
+        <v>87496</v>
+      </c>
+      <c r="K2212" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2212" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2213">
+        <v>1811</v>
+      </c>
+      <c r="B2213" t="s">
+        <v>338</v>
+      </c>
+      <c r="C2213" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2213" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2213" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2213" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2213" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2213">
+        <v>21</v>
+      </c>
+      <c r="I2213">
+        <v>800</v>
+      </c>
+      <c r="J2213">
+        <v>16829</v>
+      </c>
+      <c r="K2213" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2213" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2214">
+        <v>614</v>
+      </c>
+      <c r="B2214" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2214" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2214" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2214" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2214" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2214" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2214">
+        <v>-11</v>
+      </c>
+      <c r="I2214">
+        <v>30000</v>
+      </c>
+      <c r="J2214">
+        <v>810000</v>
+      </c>
+      <c r="K2214" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2214" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2215">
+        <v>1854</v>
+      </c>
+      <c r="B2215" t="s">
+        <v>346</v>
+      </c>
+      <c r="C2215" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2215" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2215" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2215" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2215" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2215">
+        <v>121</v>
+      </c>
+      <c r="I2215">
+        <v>60000</v>
+      </c>
+      <c r="J2215">
+        <v>7260000</v>
+      </c>
+      <c r="K2215" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2215" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2216">
+        <v>871</v>
+      </c>
+      <c r="B2216" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2216" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2216" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2216" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2216" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2216" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2216">
+        <v>36</v>
+      </c>
+      <c r="I2216">
+        <v>60000</v>
+      </c>
+      <c r="J2216">
+        <v>2159985</v>
+      </c>
+      <c r="K2216" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2216" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2217">
+        <v>2114</v>
+      </c>
+      <c r="B2217" t="s">
+        <v>398</v>
+      </c>
+      <c r="C2217" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2217" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2217" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2217" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2217" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2217">
+        <v>7</v>
+      </c>
+      <c r="I2217">
+        <v>60027</v>
+      </c>
+      <c r="J2217">
+        <v>1320048</v>
+      </c>
+      <c r="K2217" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2217" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2218">
+        <v>74</v>
+      </c>
+      <c r="B2218" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2218" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2218" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2218" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2218" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2218" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2218">
+        <v>12</v>
+      </c>
+      <c r="I2218">
+        <v>30040</v>
+      </c>
+      <c r="J2218">
+        <v>360018</v>
+      </c>
+      <c r="K2218" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2218" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2219">
+        <v>1026</v>
+      </c>
+      <c r="B2219" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2219" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2219" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2219" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2219" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2219" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2219">
+        <v>14</v>
+      </c>
+      <c r="I2219">
+        <v>3500</v>
+      </c>
+      <c r="J2219">
+        <v>48961</v>
+      </c>
+      <c r="K2219" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2219" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2220">
+        <v>1647</v>
+      </c>
+      <c r="B2220" t="s">
+        <v>320</v>
+      </c>
+      <c r="C2220" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2220" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2220" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2220" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2220" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2220">
+        <v>9</v>
+      </c>
+      <c r="I2220">
+        <v>60</v>
+      </c>
+      <c r="J2220">
+        <v>540</v>
+      </c>
+      <c r="K2220" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2220" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2221">
+        <v>540</v>
+      </c>
+      <c r="B2221" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2221" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2221" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2221" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2221" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2221" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2221">
+        <v>31</v>
+      </c>
+      <c r="I2221">
+        <v>30000</v>
+      </c>
+      <c r="J2221">
+        <v>929999</v>
+      </c>
+      <c r="K2221" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2221" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2222">
+        <v>1821</v>
+      </c>
+      <c r="B2222" t="s">
+        <v>337</v>
+      </c>
+      <c r="D2222" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2222" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2222" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2222" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2222">
+        <v>47</v>
+      </c>
+      <c r="I2222">
+        <v>3477</v>
+      </c>
+      <c r="J2222">
+        <v>115453</v>
+      </c>
+      <c r="K2222" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2222" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2223">
+        <v>-614</v>
+      </c>
+      <c r="B2223" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2223" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2223" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2223" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2223" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2223" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2223">
+        <v>27</v>
+      </c>
+      <c r="I2223">
+        <v>30000</v>
+      </c>
+      <c r="J2223">
+        <v>810006</v>
+      </c>
+      <c r="K2223" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2223" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2224">
+        <v>192</v>
+      </c>
+      <c r="B2224" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2224" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2224" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2224" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2224" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2224" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2224">
+        <v>8</v>
+      </c>
+      <c r="I2224">
+        <v>3500</v>
+      </c>
+      <c r="J2224">
+        <v>28000</v>
+      </c>
+      <c r="K2224" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2224" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2225">
+        <v>206</v>
+      </c>
+      <c r="B2225" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2225" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2225" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2225" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2225" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2225" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2225">
+        <v>58</v>
+      </c>
+      <c r="I2225">
+        <v>60</v>
+      </c>
+      <c r="J2225">
+        <v>2100</v>
+      </c>
+      <c r="K2225" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2225" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2226">
+        <v>1203</v>
+      </c>
+      <c r="B2226" t="s">
+        <v>240</v>
+      </c>
+      <c r="C2226" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2226" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2226" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2226" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2226" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2226">
+        <v>16</v>
+      </c>
+      <c r="I2226">
+        <v>5000</v>
+      </c>
+      <c r="J2226">
+        <v>80000</v>
+      </c>
+      <c r="K2226" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2226" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2227">
+        <v>1145</v>
+      </c>
+      <c r="B2227" t="s">
+        <v>229</v>
+      </c>
+      <c r="D2227" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2227" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2227" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2227" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2227">
+        <v>46</v>
+      </c>
+      <c r="I2227">
+        <v>60000</v>
+      </c>
+      <c r="J2227">
+        <v>1440000</v>
+      </c>
+      <c r="K2227" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2227" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2228">
+        <v>67</v>
+      </c>
+      <c r="B2228" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2228" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2228" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2228" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2228" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2228" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2228">
+        <v>30</v>
+      </c>
+      <c r="I2228">
+        <v>60030</v>
+      </c>
+      <c r="J2228">
+        <v>719968</v>
+      </c>
+      <c r="K2228" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2228" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2229">
+        <v>20</v>
+      </c>
+      <c r="B2229" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2229" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2229" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2229" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2229" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2229" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2229">
+        <v>-13</v>
+      </c>
+      <c r="I2229">
+        <v>30000</v>
+      </c>
+      <c r="J2229">
+        <v>360000</v>
+      </c>
+      <c r="K2229" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2229" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2230">
+        <v>1778</v>
+      </c>
+      <c r="B2230" t="s">
+        <v>336</v>
+      </c>
+      <c r="C2230" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2230" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2230" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2230" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2230" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2230">
+        <v>69</v>
+      </c>
+      <c r="I2230">
+        <v>30037</v>
+      </c>
+      <c r="J2230">
+        <v>930000</v>
+      </c>
+      <c r="K2230" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2230" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2231">
+        <v>1250</v>
+      </c>
+      <c r="B2231" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2231" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2231" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2231" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2231" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2231" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2231">
+        <v>-2</v>
+      </c>
+      <c r="I2231">
+        <v>30000</v>
+      </c>
+      <c r="J2231">
+        <v>750000</v>
+      </c>
+      <c r="K2231" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2231" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2232">
+        <v>1758</v>
+      </c>
+      <c r="B2232" t="s">
+        <v>332</v>
+      </c>
+      <c r="C2232" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2232" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2232" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2232" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2232" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2232">
+        <v>11</v>
+      </c>
+      <c r="I2232">
+        <v>3500</v>
+      </c>
+      <c r="J2232">
+        <v>38506</v>
+      </c>
+      <c r="K2232" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2232" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2233">
+        <v>444</v>
+      </c>
+      <c r="B2233" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2233" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2233" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2233" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2233" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2233" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2233">
+        <v>24</v>
+      </c>
+      <c r="I2233">
+        <v>3500</v>
+      </c>
+      <c r="J2233">
+        <v>84028</v>
+      </c>
+      <c r="K2233" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2233" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2234">
+        <v>1157</v>
+      </c>
+      <c r="B2234" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2234" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2234" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2234" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2234" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2234" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2234">
+        <v>30</v>
+      </c>
+      <c r="I2234">
+        <v>800</v>
+      </c>
+      <c r="J2234">
+        <v>24000</v>
+      </c>
+      <c r="K2234" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2234" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2235">
+        <v>2074</v>
+      </c>
+      <c r="B2235" t="s">
+        <v>391</v>
+      </c>
+      <c r="C2235" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2235" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2235" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2235" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2235" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2235">
+        <v>19</v>
+      </c>
+      <c r="I2235">
+        <v>60</v>
+      </c>
+      <c r="J2235">
+        <v>1143</v>
+      </c>
+      <c r="K2235" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2235" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2236">
+        <v>-1220</v>
+      </c>
+      <c r="B2236" t="s">
+        <v>235</v>
+      </c>
+      <c r="C2236" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2236" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2236" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2236" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2236" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2236">
+        <v>28</v>
+      </c>
+      <c r="I2236">
+        <v>60000</v>
+      </c>
+      <c r="J2236">
+        <v>1680000</v>
+      </c>
+      <c r="K2236" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2236" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2237">
+        <v>81</v>
+      </c>
+      <c r="B2237" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2237" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2237" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2237" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2237" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2237" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2237">
+        <v>8</v>
+      </c>
+      <c r="I2237">
+        <v>4969</v>
+      </c>
+      <c r="J2237">
+        <v>40000</v>
+      </c>
+      <c r="K2237" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2237" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2238">
+        <v>81</v>
+      </c>
+      <c r="B2238" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2238" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2238" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2238" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2238" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2238" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2238">
+        <v>-36</v>
+      </c>
+      <c r="I2238">
+        <v>5000</v>
+      </c>
+      <c r="J2238">
+        <v>39973</v>
+      </c>
+      <c r="K2238" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2238" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2239">
+        <v>700</v>
+      </c>
+      <c r="B2239" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2239" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2239" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2239" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2239" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2239" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2239">
+        <v>44</v>
+      </c>
+      <c r="I2239">
+        <v>60</v>
+      </c>
+      <c r="J2239">
+        <v>2340</v>
+      </c>
+      <c r="L2239" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2240">
+        <v>633</v>
+      </c>
+      <c r="B2240" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2240" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2240" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2240" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2240" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2240" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2240">
+        <v>23</v>
+      </c>
+      <c r="I2240">
+        <v>5000</v>
+      </c>
+      <c r="J2240">
+        <v>115000</v>
+      </c>
+      <c r="K2240" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2240" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2241">
+        <v>1458</v>
+      </c>
+      <c r="B2241" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2241" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2241" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2241" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2241" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2241" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2241">
+        <v>36</v>
+      </c>
+      <c r="I2241">
+        <v>3500</v>
+      </c>
+      <c r="J2241">
+        <v>126000</v>
+      </c>
+      <c r="K2241" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2241" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2242">
+        <v>1971</v>
+      </c>
+      <c r="B2242" t="s">
+        <v>373</v>
+      </c>
+      <c r="C2242" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2242" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2242" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2242" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2242" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2242">
+        <v>0</v>
+      </c>
+      <c r="I2242">
+        <v>59996</v>
+      </c>
+      <c r="J2242">
+        <v>2279952</v>
+      </c>
+      <c r="K2242" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2242" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2243">
+        <v>297</v>
+      </c>
+      <c r="B2243" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2243" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2243" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2243" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2243" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2243" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2243">
+        <v>61</v>
+      </c>
+      <c r="I2243">
+        <v>60000</v>
+      </c>
+      <c r="J2243">
+        <v>1379970</v>
+      </c>
+      <c r="K2243" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2243" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2244">
+        <v>-1997</v>
+      </c>
+      <c r="B2244" t="s">
+        <v>372</v>
+      </c>
+      <c r="C2244" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2244" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2244" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2244" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2244" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2244">
+        <v>5</v>
+      </c>
+      <c r="I2244">
+        <v>806</v>
+      </c>
+      <c r="J2244">
+        <v>4000</v>
+      </c>
+      <c r="K2244" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2244" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2245">
+        <v>740</v>
+      </c>
+      <c r="B2245" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2245" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2245" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2245" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2245" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2245" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2245">
+        <v>13</v>
+      </c>
+      <c r="I2245">
+        <v>30000</v>
+      </c>
+      <c r="J2245">
+        <v>390000</v>
+      </c>
+      <c r="K2245" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2245" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2246">
+        <v>1637</v>
+      </c>
+      <c r="B2246" t="s">
+        <v>312</v>
+      </c>
+      <c r="C2246" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2246" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2246" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2246" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2246" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2246">
+        <v>10</v>
+      </c>
+      <c r="I2246">
+        <v>800</v>
+      </c>
+      <c r="J2246">
+        <v>8000</v>
+      </c>
+      <c r="K2246" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2246" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2247">
+        <v>-32</v>
+      </c>
+      <c r="B2247" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2247" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2247" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2247" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2247" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2247" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2247">
+        <v>51</v>
+      </c>
+      <c r="I2247">
+        <v>30000</v>
+      </c>
+      <c r="J2247">
+        <v>1530000</v>
+      </c>
+      <c r="K2247" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2247" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2248">
+        <v>207</v>
+      </c>
+      <c r="B2248" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2248" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2248" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2248" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2248" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2248" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2248">
+        <v>24</v>
+      </c>
+      <c r="I2248">
+        <v>5050</v>
+      </c>
+      <c r="J2248">
+        <v>120000</v>
+      </c>
+      <c r="K2248" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2248" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2249">
+        <v>1914</v>
+      </c>
+      <c r="B2249" t="s">
+        <v>358</v>
+      </c>
+      <c r="C2249" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2249" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2249" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2249" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2249" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2249">
+        <v>7</v>
+      </c>
+      <c r="I2249">
+        <v>3493</v>
+      </c>
+      <c r="J2249">
+        <v>24500</v>
+      </c>
+      <c r="K2249" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2249" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2250">
+        <v>1720</v>
+      </c>
+      <c r="B2250" t="s">
+        <v>326</v>
+      </c>
+      <c r="C2250" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2250" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2250" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2250" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2250" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2250">
+        <v>19</v>
+      </c>
+      <c r="I2250">
+        <v>20</v>
+      </c>
+      <c r="J2250">
+        <v>1140</v>
+      </c>
+      <c r="K2250" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2250" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2251">
+        <v>1438</v>
+      </c>
+      <c r="B2251" t="s">
+        <v>285</v>
+      </c>
+      <c r="C2251" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2251" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2251" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2251" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2251" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2251">
+        <v>26</v>
+      </c>
+      <c r="I2251">
+        <v>3475</v>
+      </c>
+      <c r="J2251">
+        <v>91013</v>
+      </c>
+      <c r="K2251" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2251" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2252">
+        <v>-816</v>
+      </c>
+      <c r="B2252" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2252" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2252" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2252" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2252" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2252" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2252">
+        <v>16</v>
+      </c>
+      <c r="I2252">
+        <v>30000</v>
+      </c>
+      <c r="J2252">
+        <v>480040</v>
+      </c>
+      <c r="K2252" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2252" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2253">
+        <v>1520</v>
+      </c>
+      <c r="B2253" t="s">
+        <v>293</v>
+      </c>
+      <c r="C2253" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2253" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2253" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2253" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2253" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2253">
+        <v>30</v>
+      </c>
+      <c r="I2253">
+        <v>30000</v>
+      </c>
+      <c r="J2253">
+        <v>899968</v>
+      </c>
+      <c r="K2253" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2253" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2254">
+        <v>859</v>
+      </c>
+      <c r="B2254" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2254" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2254" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2254" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2254" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2254" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2254">
+        <v>34</v>
+      </c>
+      <c r="I2254">
+        <v>60000</v>
+      </c>
+      <c r="J2254">
+        <v>2040000</v>
+      </c>
+      <c r="K2254" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2254" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2255">
+        <v>363</v>
+      </c>
+      <c r="B2255" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2255" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2255" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2255" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2255" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2255" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2255">
+        <v>76</v>
+      </c>
+      <c r="I2255">
+        <v>5000</v>
+      </c>
+      <c r="J2255">
+        <v>380000</v>
+      </c>
+      <c r="K2255" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2255" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2256">
+        <v>288</v>
+      </c>
+      <c r="B2256" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2256" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2256" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2256" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2256" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2256" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2256">
+        <v>30</v>
+      </c>
+      <c r="I2256">
+        <v>3489</v>
+      </c>
+      <c r="J2256">
+        <v>105000</v>
+      </c>
+      <c r="K2256" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2256" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2257">
+        <v>15</v>
+      </c>
+      <c r="B2257" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2257" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2257" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2257" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2257" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2257" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2257">
+        <v>33</v>
+      </c>
+      <c r="I2257">
+        <v>5024</v>
+      </c>
+      <c r="J2257">
+        <v>165000</v>
+      </c>
+      <c r="K2257" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2258">
+        <v>1811</v>
+      </c>
+      <c r="B2258" t="s">
+        <v>344</v>
+      </c>
+      <c r="C2258" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2258" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2258" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2258" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2258" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2258">
+        <v>73</v>
+      </c>
+      <c r="I2258">
+        <v>3500</v>
+      </c>
+      <c r="J2258">
+        <v>255500</v>
+      </c>
+      <c r="K2258" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2258" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2259">
+        <v>1316</v>
+      </c>
+      <c r="B2259" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2259" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2259" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2259" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2259" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2259" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2259">
+        <v>47</v>
+      </c>
+      <c r="I2259">
+        <v>30000</v>
+      </c>
+      <c r="J2259">
+        <v>1710000</v>
+      </c>
+      <c r="K2259" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2259" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2260">
+        <v>-1960</v>
+      </c>
+      <c r="B2260" t="s">
+        <v>366</v>
+      </c>
+      <c r="C2260" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2260" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2260" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2260" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2260" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2260">
+        <v>11</v>
+      </c>
+      <c r="I2260">
+        <v>20</v>
+      </c>
+      <c r="J2260">
+        <v>660</v>
+      </c>
+      <c r="K2260" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2260" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2261">
+        <v>391</v>
+      </c>
+      <c r="B2261" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2261" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2261" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2261" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2261" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2261">
+        <v>13</v>
+      </c>
+      <c r="I2261">
+        <v>59980</v>
+      </c>
+      <c r="J2261">
+        <v>780000</v>
+      </c>
+      <c r="K2261" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2261" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2262">
+        <v>1218</v>
+      </c>
+      <c r="B2262" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2262" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2262" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2262" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2262" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2262" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2262">
+        <v>22</v>
+      </c>
+      <c r="I2262">
+        <v>3500</v>
+      </c>
+      <c r="J2262">
+        <v>77000</v>
+      </c>
+      <c r="K2262" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2262" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2263">
+        <v>452</v>
+      </c>
+      <c r="B2263" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2263" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2263" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2263" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2263" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2263" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2263">
+        <v>40</v>
+      </c>
+      <c r="I2263">
+        <v>30000</v>
+      </c>
+      <c r="J2263">
+        <v>1200000</v>
+      </c>
+      <c r="K2263" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2263" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2264">
+        <v>934</v>
+      </c>
+      <c r="B2264" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2264" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2264" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2264" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2264" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2264" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2264">
+        <v>26</v>
+      </c>
+      <c r="I2264">
+        <v>60</v>
+      </c>
+      <c r="J2264">
+        <v>1560</v>
+      </c>
+      <c r="K2264" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2264" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2265">
+        <v>1641</v>
+      </c>
+      <c r="B2265" t="s">
+        <v>313</v>
+      </c>
+      <c r="C2265" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2265" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2265" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2265" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2265" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2265">
+        <v>35</v>
+      </c>
+      <c r="I2265">
+        <v>5000</v>
+      </c>
+      <c r="J2265">
+        <v>45000</v>
+      </c>
+      <c r="K2265" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2265" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2266">
+        <v>813</v>
+      </c>
+      <c r="B2266" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2266" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2266" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2266" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2266" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2266" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2266">
+        <v>26</v>
+      </c>
+      <c r="I2266">
+        <v>5000</v>
+      </c>
+      <c r="J2266">
+        <v>130021</v>
+      </c>
+      <c r="L2266" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2267">
+        <v>425</v>
+      </c>
+      <c r="B2267" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2267" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2267" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2267" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2267" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2267" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2267">
+        <v>9</v>
+      </c>
+      <c r="I2267">
+        <v>60</v>
+      </c>
+      <c r="J2267">
+        <v>960</v>
+      </c>
+      <c r="K2267" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2267" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2268">
+        <v>1196</v>
+      </c>
+      <c r="B2268" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2268" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2268" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2268" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2268" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2268" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2268">
+        <v>55</v>
+      </c>
+      <c r="I2268">
+        <v>3500</v>
+      </c>
+      <c r="J2268">
+        <v>192455</v>
+      </c>
+      <c r="K2268" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2268" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2269">
+        <v>523</v>
+      </c>
+      <c r="B2269" t="s">
+        <v>127</v>
+      </c>
+      <c r="C2269" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2269" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2269" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2269" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2269" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2269">
+        <v>8</v>
+      </c>
+      <c r="I2269">
+        <v>60000</v>
+      </c>
+      <c r="J2269">
+        <v>1979951</v>
+      </c>
+      <c r="K2269" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B2270" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2270" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2270" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2270" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2270" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2270" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2270">
+        <v>36</v>
+      </c>
+      <c r="I2270">
+        <v>60</v>
+      </c>
+      <c r="J2270">
+        <v>2169</v>
+      </c>
+      <c r="K2270" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2270" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2271">
+        <v>1072</v>
+      </c>
+      <c r="B2271" t="s">
+        <v>221</v>
+      </c>
+      <c r="C2271" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2271" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2271" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2271" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2271" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2271">
+        <v>20</v>
+      </c>
+      <c r="I2271">
+        <v>800</v>
+      </c>
+      <c r="J2271">
+        <v>16009</v>
+      </c>
+      <c r="K2271" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2271" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2272">
+        <v>676</v>
+      </c>
+      <c r="B2272" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2272" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2272" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2272" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2272" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2272" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2272">
+        <v>31</v>
+      </c>
+      <c r="I2272">
+        <v>30000</v>
+      </c>
+      <c r="J2272">
+        <v>930023</v>
+      </c>
+      <c r="K2272" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2272" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2273" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2273">
+        <v>1451</v>
+      </c>
+      <c r="B2273" t="s">
+        <v>281</v>
+      </c>
+      <c r="C2273" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2273" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2273" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2273" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2273" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2273">
+        <v>13</v>
+      </c>
+      <c r="I2273">
+        <v>800</v>
+      </c>
+      <c r="J2273">
+        <v>19200</v>
+      </c>
+      <c r="K2273" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2273" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2274" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2274">
+        <v>1567</v>
+      </c>
+      <c r="B2274" t="s">
+        <v>301</v>
+      </c>
+      <c r="C2274" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2274" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2274" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2274" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2274" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2274">
+        <v>34</v>
+      </c>
+      <c r="I2274">
+        <v>60000</v>
+      </c>
+      <c r="J2274">
+        <v>2040000</v>
+      </c>
+      <c r="K2274" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2274" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2275" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2275">
+        <v>1523</v>
+      </c>
+      <c r="B2275" t="s">
+        <v>300</v>
+      </c>
+      <c r="C2275" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2275" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2275" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2275" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2275" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2275">
+        <v>24</v>
+      </c>
+      <c r="I2275">
+        <v>3500</v>
+      </c>
+      <c r="J2275">
+        <v>112010</v>
+      </c>
+      <c r="K2275" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2275" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2276">
+        <v>454</v>
+      </c>
+      <c r="B2276" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2276" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2276" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2276" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2276" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2276">
+        <v>13</v>
+      </c>
+      <c r="I2276">
+        <v>3500</v>
+      </c>
+      <c r="J2276">
+        <v>45500</v>
+      </c>
+      <c r="K2276" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2276" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2277" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2277">
+        <v>-856</v>
+      </c>
+      <c r="B2277" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2277" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2277" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2277" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2277" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2277" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2277">
+        <v>30</v>
+      </c>
+      <c r="I2277">
+        <v>60000</v>
+      </c>
+      <c r="J2277">
+        <v>1800016</v>
+      </c>
+      <c r="K2277" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2277" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2278">
+        <v>1241</v>
+      </c>
+      <c r="B2278" t="s">
+        <v>246</v>
+      </c>
+      <c r="C2278" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2278" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2278" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2278" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2278" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2278">
+        <v>22</v>
+      </c>
+      <c r="I2278">
+        <v>800</v>
+      </c>
+      <c r="J2278">
+        <v>17600</v>
+      </c>
+      <c r="K2278" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2278" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2279">
+        <v>931</v>
+      </c>
+      <c r="B2279" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2279" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2279" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2279" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2279" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2279" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2279">
+        <v>40</v>
+      </c>
+      <c r="I2279">
+        <v>30000</v>
+      </c>
+      <c r="J2279">
+        <v>2220000</v>
+      </c>
+      <c r="K2279" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2279" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2280">
+        <v>366</v>
+      </c>
+      <c r="B2280" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2280" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2280" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2280" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2280" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2280" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2280">
+        <v>28</v>
+      </c>
+      <c r="I2280">
+        <v>3500</v>
+      </c>
+      <c r="J2280">
+        <v>98000</v>
+      </c>
+      <c r="K2280" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2280" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2281" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2281">
+        <v>2007</v>
+      </c>
+      <c r="B2281" t="s">
+        <v>380</v>
+      </c>
+      <c r="C2281" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2281" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2281" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2281" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2281" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2281">
+        <v>17</v>
+      </c>
+      <c r="I2281">
+        <v>30000</v>
+      </c>
+      <c r="J2281">
+        <v>750000</v>
+      </c>
+      <c r="K2281" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2281" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2282">
+        <v>56</v>
+      </c>
+      <c r="B2282" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2282" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2282" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2282" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2282" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2282" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2282">
+        <v>26</v>
+      </c>
+      <c r="I2282">
+        <v>30000</v>
+      </c>
+      <c r="J2282">
+        <v>960000</v>
+      </c>
+      <c r="K2282" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2282" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2283">
+        <v>286</v>
+      </c>
+      <c r="B2283" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2283" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2283" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2283" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2283" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2283" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2283">
+        <v>-11</v>
+      </c>
+      <c r="I2283">
+        <v>60</v>
+      </c>
+      <c r="J2283">
+        <v>1020</v>
+      </c>
+      <c r="K2283" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2283" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2284">
+        <v>310</v>
+      </c>
+      <c r="B2284" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2284" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2284" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2284" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2284" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2284" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2284">
+        <v>-7</v>
+      </c>
+      <c r="I2284">
+        <v>60</v>
+      </c>
+      <c r="J2284">
+        <v>1797</v>
+      </c>
+      <c r="K2284" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2284" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2285">
+        <v>1146</v>
+      </c>
+      <c r="B2285" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2285" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2285" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2285" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2285" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2285" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2285">
+        <v>38</v>
+      </c>
+      <c r="I2285">
+        <v>3500</v>
+      </c>
+      <c r="J2285">
+        <v>133000</v>
+      </c>
+      <c r="K2285" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2285" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2286">
+        <v>2190</v>
+      </c>
+      <c r="B2286" t="s">
+        <v>404</v>
+      </c>
+      <c r="D2286" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2286" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2286" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2286" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2286">
+        <v>53</v>
+      </c>
+      <c r="I2286">
+        <v>3500</v>
+      </c>
+      <c r="J2286">
+        <v>59500</v>
+      </c>
+      <c r="K2286" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2286" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2287">
+        <v>-1508</v>
+      </c>
+      <c r="B2287" t="s">
+        <v>291</v>
+      </c>
+      <c r="C2287" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2287" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2287" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2287" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2287" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2287">
+        <v>8</v>
+      </c>
+      <c r="I2287">
+        <v>30030</v>
+      </c>
+      <c r="J2287">
+        <v>240021</v>
+      </c>
+      <c r="K2287" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2287" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2288">
+        <v>560</v>
+      </c>
+      <c r="B2288" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2288" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2288" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2288" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2288" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2288" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2288">
+        <v>82</v>
+      </c>
+      <c r="I2288">
+        <v>30000</v>
+      </c>
+      <c r="J2288">
+        <v>1980030</v>
+      </c>
+      <c r="K2288" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2288" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2289">
+        <v>1028</v>
+      </c>
+      <c r="B2289" t="s">
+        <v>211</v>
+      </c>
+      <c r="C2289" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2289" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2289" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2289" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2289" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2289">
+        <v>33</v>
+      </c>
+      <c r="I2289">
+        <v>30000</v>
+      </c>
+      <c r="J2289">
+        <v>990000</v>
+      </c>
+      <c r="K2289" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2289" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2290">
+        <v>399</v>
+      </c>
+      <c r="B2290" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2290" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2290" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2290" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2290" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2290" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2290">
+        <v>5000</v>
+      </c>
+      <c r="J2290">
+        <v>109968</v>
+      </c>
+      <c r="K2290" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2290" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2291">
+        <v>868</v>
+      </c>
+      <c r="B2291" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2291" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2291" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2291" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2291" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2291" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2291">
+        <v>7</v>
+      </c>
+      <c r="I2291">
+        <v>5000</v>
+      </c>
+      <c r="J2291">
+        <v>35000</v>
+      </c>
+      <c r="K2291" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2291" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2292">
+        <v>352</v>
+      </c>
+      <c r="B2292" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2292" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2292" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2292" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2292" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2292" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2292">
+        <v>13</v>
+      </c>
+      <c r="I2292">
+        <v>30013</v>
+      </c>
+      <c r="J2292">
+        <v>390000</v>
+      </c>
+      <c r="K2292" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2292" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2293">
+        <v>1727</v>
+      </c>
+      <c r="B2293" t="s">
+        <v>327</v>
+      </c>
+      <c r="C2293" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2293" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2293" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2293" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2293" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2293">
+        <v>7</v>
+      </c>
+      <c r="I2293">
+        <v>776</v>
+      </c>
+      <c r="J2293">
+        <v>5600</v>
+      </c>
+      <c r="K2293" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2293" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2294">
+        <v>-661</v>
+      </c>
+      <c r="B2294" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2294" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2294" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2294" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2294" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2294" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2294">
+        <v>62</v>
+      </c>
+      <c r="I2294">
+        <v>30021</v>
+      </c>
+      <c r="J2294">
+        <v>660047</v>
+      </c>
+      <c r="K2294" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2294" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2295">
+        <v>808</v>
+      </c>
+      <c r="B2295" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2295" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2295" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2295" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2295" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2295" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2295">
+        <v>-14</v>
+      </c>
+      <c r="I2295">
+        <v>3500</v>
+      </c>
+      <c r="J2295">
+        <v>21000</v>
+      </c>
+      <c r="K2295" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2295" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2296" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2296">
+        <v>1803</v>
+      </c>
+      <c r="B2296" t="s">
+        <v>340</v>
+      </c>
+      <c r="C2296" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2296" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2296" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2296" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2296" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2296">
+        <v>14</v>
+      </c>
+      <c r="I2296">
+        <v>5001</v>
+      </c>
+      <c r="J2296">
+        <v>35024</v>
+      </c>
+      <c r="K2296" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2296" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2297">
+        <v>47</v>
+      </c>
+      <c r="B2297" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2297" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2297" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2297" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2297" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2297" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2297">
+        <v>5</v>
+      </c>
+      <c r="I2297">
+        <v>800</v>
+      </c>
+      <c r="J2297">
+        <v>4000</v>
+      </c>
+      <c r="K2297" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2297" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2298">
+        <v>496</v>
+      </c>
+      <c r="B2298" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2298" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2298" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2298" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2298" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2298" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2298">
+        <v>21</v>
+      </c>
+      <c r="I2298">
+        <v>3500</v>
+      </c>
+      <c r="J2298">
+        <v>73526</v>
+      </c>
+      <c r="K2298" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2298" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2299">
+        <v>1053</v>
+      </c>
+      <c r="B2299" t="s">
+        <v>215</v>
+      </c>
+      <c r="C2299" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2299" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2299" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2299" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2299" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2299">
+        <v>53</v>
+      </c>
+      <c r="I2299">
+        <v>5000</v>
+      </c>
+      <c r="J2299">
+        <v>379989</v>
+      </c>
+      <c r="K2299" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2299" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2300">
+        <v>1821</v>
+      </c>
+      <c r="B2300" t="s">
+        <v>340</v>
+      </c>
+      <c r="C2300" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2300" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2300" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2300" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2300" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2300">
+        <v>7</v>
+      </c>
+      <c r="I2300">
+        <v>4972</v>
+      </c>
+      <c r="J2300">
+        <v>35000</v>
+      </c>
+      <c r="K2300" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2300" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2301">
+        <v>40</v>
+      </c>
+      <c r="B2301" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2301" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2301" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2301" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2301" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2301" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2301">
+        <v>10</v>
+      </c>
+      <c r="I2301">
+        <v>60</v>
+      </c>
+      <c r="J2301">
+        <v>600</v>
+      </c>
+      <c r="K2301" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2301" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2302">
+        <v>659</v>
+      </c>
+      <c r="B2302" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2302" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2302" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2302" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2302" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2302" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2302">
+        <v>32</v>
+      </c>
+      <c r="I2302">
+        <v>770</v>
+      </c>
+      <c r="J2302">
+        <v>25600</v>
+      </c>
+      <c r="K2302" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2302" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2303">
+        <v>1686</v>
+      </c>
+      <c r="B2303" t="s">
+        <v>318</v>
+      </c>
+      <c r="C2303" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2303" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2303" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2303" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2303" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2303">
+        <v>20</v>
+      </c>
+      <c r="I2303">
+        <v>60</v>
+      </c>
+      <c r="J2303">
+        <v>1200</v>
+      </c>
+      <c r="K2303" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2303" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2304">
+        <v>776</v>
+      </c>
+      <c r="B2304" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2304" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2304" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2304" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2304" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2304" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2304">
+        <v>13</v>
+      </c>
+      <c r="I2304">
+        <v>30000</v>
+      </c>
+      <c r="J2304">
+        <v>690000</v>
+      </c>
+      <c r="K2304" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2304" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2305">
+        <v>292</v>
+      </c>
+      <c r="B2305" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2305" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2305" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2305" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2305" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2305">
+        <v>7</v>
+      </c>
+      <c r="I2305">
+        <v>3454</v>
+      </c>
+      <c r="J2305">
+        <v>24515</v>
+      </c>
+      <c r="K2305" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2305" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2306">
+        <v>551</v>
+      </c>
+      <c r="B2306" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2306" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2306" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2306" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2306" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2306" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2306">
+        <v>58</v>
+      </c>
+      <c r="I2306">
+        <v>800</v>
+      </c>
+      <c r="J2306">
+        <v>26400</v>
+      </c>
+      <c r="K2306" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2306" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2307">
+        <v>300</v>
+      </c>
+      <c r="B2307" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2307" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2307" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2307" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2307" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2307" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2307">
+        <v>23</v>
+      </c>
+      <c r="I2307">
+        <v>3500</v>
+      </c>
+      <c r="J2307">
+        <v>80455</v>
+      </c>
+      <c r="K2307" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2307" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2308">
+        <v>460</v>
+      </c>
+      <c r="B2308" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2308" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2308" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2308" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2308" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2308" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2308">
+        <v>46</v>
+      </c>
+      <c r="I2308">
+        <v>60000</v>
+      </c>
+      <c r="J2308">
+        <v>1980000</v>
+      </c>
+      <c r="K2308" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2308" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2309">
+        <v>1464</v>
+      </c>
+      <c r="B2309" t="s">
+        <v>283</v>
+      </c>
+      <c r="C2309" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2309" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2309" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2309" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2309" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2309">
+        <v>18</v>
+      </c>
+      <c r="I2309">
+        <v>3500</v>
+      </c>
+      <c r="J2309">
+        <v>63000</v>
+      </c>
+      <c r="K2309" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2309" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2310" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2310">
+        <v>-1997</v>
+      </c>
+      <c r="B2310" t="s">
+        <v>372</v>
+      </c>
+      <c r="C2310" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2310" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2310" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2310" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2310" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2310">
+        <v>55</v>
+      </c>
+      <c r="I2310">
+        <v>800</v>
+      </c>
+      <c r="J2310">
+        <v>3991</v>
+      </c>
+      <c r="K2310" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2310" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2311">
+        <v>294</v>
+      </c>
+      <c r="B2311" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2311" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2311" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2311" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2311" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2311" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2311">
+        <v>-25</v>
+      </c>
+      <c r="I2311">
+        <v>3540</v>
+      </c>
+      <c r="J2311">
+        <v>87500</v>
+      </c>
+      <c r="K2311" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2311" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2312">
+        <v>1125</v>
+      </c>
+      <c r="B2312" t="s">
+        <v>227</v>
+      </c>
+      <c r="C2312" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2312" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2312" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2312" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2312" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2312">
+        <v>35</v>
+      </c>
+      <c r="I2312">
+        <v>4967</v>
+      </c>
+      <c r="J2312">
+        <v>75040</v>
+      </c>
+      <c r="K2312" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2312" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2313">
+        <v>1251</v>
+      </c>
+      <c r="B2313" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2313" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2313" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2313" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2313" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2313" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2313">
+        <v>128</v>
+      </c>
+      <c r="I2313">
+        <v>5000</v>
+      </c>
+      <c r="J2313">
+        <v>470000</v>
+      </c>
+      <c r="K2313" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2313" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2314">
+        <v>-500</v>
+      </c>
+      <c r="B2314" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2314" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2314" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2314" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2314" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2314" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2314">
+        <v>63</v>
+      </c>
+      <c r="I2314">
+        <v>60022</v>
+      </c>
+      <c r="J2314">
+        <v>3000000</v>
+      </c>
+      <c r="K2314" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2314" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2315">
+        <v>264</v>
+      </c>
+      <c r="B2315" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2315" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2315" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2315" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2315" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2315" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2315">
+        <v>35</v>
+      </c>
+      <c r="I2315">
+        <v>5006</v>
+      </c>
+      <c r="J2315">
+        <v>174985</v>
+      </c>
+      <c r="K2315" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2315" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2316" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2316">
+        <v>-710</v>
+      </c>
+      <c r="B2316" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2316" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2316" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2316" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2316" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2316" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2316">
+        <v>62</v>
+      </c>
+      <c r="I2316">
+        <v>30013</v>
+      </c>
+      <c r="J2316">
+        <v>1859990</v>
+      </c>
+      <c r="K2316" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2316" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2317">
+        <v>1759</v>
+      </c>
+      <c r="B2317" t="s">
+        <v>340</v>
+      </c>
+      <c r="C2317" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2317" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2317" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2317" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2317" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2317">
+        <v>19</v>
+      </c>
+      <c r="I2317">
+        <v>60</v>
+      </c>
+      <c r="J2317">
+        <v>1140</v>
+      </c>
+      <c r="K2317" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2317" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2318" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2318">
+        <v>1358</v>
+      </c>
+      <c r="B2318" t="s">
+        <v>266</v>
+      </c>
+      <c r="C2318" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2318" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2318" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2318" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2318" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2318">
+        <v>37</v>
+      </c>
+      <c r="I2318">
+        <v>30031</v>
+      </c>
+      <c r="J2318">
+        <v>1110000</v>
+      </c>
+      <c r="K2318" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2318" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2319">
+        <v>-28</v>
+      </c>
+      <c r="B2319" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2319" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2319" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2319" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2319" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2319" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2319">
+        <v>17</v>
+      </c>
+      <c r="J2319">
+        <v>1020</v>
+      </c>
+      <c r="K2319" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2319" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2320" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2320">
+        <v>-378</v>
+      </c>
+      <c r="B2320" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2320" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2320" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2320" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2320" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2320" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2320">
+        <v>68</v>
+      </c>
+      <c r="I2320">
+        <v>3500</v>
+      </c>
+      <c r="J2320">
+        <v>132986</v>
+      </c>
+      <c r="K2320" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2320" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2321" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2321">
+        <v>1682</v>
+      </c>
+      <c r="B2321" t="s">
+        <v>320</v>
+      </c>
+      <c r="C2321" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2321" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2321" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2321" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2321" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2321">
+        <v>-12</v>
+      </c>
+      <c r="I2321">
+        <v>29993</v>
+      </c>
+      <c r="J2321">
+        <v>450000</v>
+      </c>
+      <c r="K2321" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2321" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2322" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2322">
+        <v>-1921</v>
+      </c>
+      <c r="B2322" t="s">
+        <v>360</v>
+      </c>
+      <c r="C2322" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2322" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2322" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2322" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2322" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2322">
+        <v>38</v>
+      </c>
+      <c r="I2322">
+        <v>60000</v>
+      </c>
+      <c r="J2322">
+        <v>2279957</v>
+      </c>
+      <c r="K2322" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2322" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2323">
+        <v>-1470</v>
+      </c>
+      <c r="B2323" t="s">
+        <v>284</v>
+      </c>
+      <c r="C2323" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2323" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2323" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2323" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2323" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2323">
+        <v>18</v>
+      </c>
+      <c r="I2323">
+        <v>3500</v>
+      </c>
+      <c r="J2323">
+        <v>62993</v>
+      </c>
+      <c r="K2323" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2323" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2324">
+        <v>1557</v>
+      </c>
+      <c r="B2324" t="s">
+        <v>300</v>
+      </c>
+      <c r="C2324" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2324" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2324" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2324" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2324" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2324">
+        <v>39</v>
+      </c>
+      <c r="I2324">
+        <v>5000</v>
+      </c>
+      <c r="J2324">
+        <v>194983</v>
+      </c>
+      <c r="K2324" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2324" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2325" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2325">
+        <v>-1599</v>
+      </c>
+      <c r="B2325" t="s">
+        <v>306</v>
+      </c>
+      <c r="C2325" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2325" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2325" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2325" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2325" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2325">
+        <v>29</v>
+      </c>
+      <c r="I2325">
+        <v>5000</v>
+      </c>
+      <c r="J2325">
+        <v>145000</v>
+      </c>
+      <c r="K2325" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2325" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2326" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2326">
+        <v>-521</v>
+      </c>
+      <c r="B2326" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2326" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2326" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2326" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2326" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2326">
+        <v>35</v>
+      </c>
+      <c r="I2326">
+        <v>800</v>
+      </c>
+      <c r="J2326">
+        <v>27962</v>
+      </c>
+      <c r="K2326" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2326" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2327" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2327">
+        <v>1253</v>
+      </c>
+      <c r="B2327" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2327" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2327" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2327" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2327" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2327" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2327">
+        <v>-2</v>
+      </c>
+      <c r="I2327">
+        <v>800</v>
+      </c>
+      <c r="J2327">
+        <v>18421</v>
+      </c>
+      <c r="K2327" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2327" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2328" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2328">
+        <v>2082</v>
+      </c>
+      <c r="B2328" t="s">
+        <v>386</v>
+      </c>
+      <c r="C2328" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2328" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2328" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2328" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2328" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2328">
+        <v>70</v>
+      </c>
+      <c r="I2328">
+        <v>3483</v>
+      </c>
+      <c r="J2328">
+        <v>245000</v>
+      </c>
+      <c r="K2328" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2328" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2329" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2329">
+        <v>697</v>
+      </c>
+      <c r="B2329" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2329" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2329" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2329" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2329" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2329" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2329">
+        <v>35</v>
+      </c>
+      <c r="I2329">
+        <v>60000</v>
+      </c>
+      <c r="J2329">
+        <v>2099986</v>
+      </c>
+      <c r="K2329" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2329" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2330" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2330">
+        <v>1391</v>
+      </c>
+      <c r="B2330" t="s">
+        <v>265</v>
+      </c>
+      <c r="C2330" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2330" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2330" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2330" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2330" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2330">
+        <v>50</v>
+      </c>
+      <c r="I2330">
+        <v>27</v>
+      </c>
+      <c r="J2330">
+        <v>840</v>
+      </c>
+      <c r="K2330" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2330" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2331" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2331">
+        <v>500</v>
+      </c>
+      <c r="B2331" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2331" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2331" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2331" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2331" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2331" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2331">
+        <v>38</v>
+      </c>
+      <c r="I2331">
+        <v>30000</v>
+      </c>
+      <c r="J2331">
+        <v>1139979</v>
+      </c>
+      <c r="K2331" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2331" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2332" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2332">
+        <v>1956</v>
+      </c>
+      <c r="B2332" t="s">
+        <v>373</v>
+      </c>
+      <c r="C2332" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2332" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2332" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2332" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2332" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2332">
+        <v>20</v>
+      </c>
+      <c r="I2332">
+        <v>3500</v>
+      </c>
+      <c r="J2332">
+        <v>69990</v>
+      </c>
+      <c r="K2332" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2332" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2333" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2333">
+        <v>783</v>
+      </c>
+      <c r="B2333" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2333" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2333" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2333" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2333" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2333" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2333">
+        <v>17</v>
+      </c>
+      <c r="I2333">
+        <v>849</v>
+      </c>
+      <c r="J2333">
+        <v>13600</v>
+      </c>
+      <c r="K2333" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2333" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2334" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2334">
+        <v>2162</v>
+      </c>
+      <c r="B2334" t="s">
+        <v>400</v>
+      </c>
+      <c r="C2334" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2334" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2334" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2334" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2334" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2334">
+        <v>14</v>
+      </c>
+      <c r="I2334">
+        <v>30000</v>
+      </c>
+      <c r="J2334">
+        <v>1170000</v>
+      </c>
+      <c r="K2334" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2334" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2335" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2335">
+        <v>-116</v>
+      </c>
+      <c r="B2335" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2335" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2335" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2335" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2335" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2335" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2335">
+        <v>12</v>
+      </c>
+      <c r="I2335">
+        <v>30000</v>
+      </c>
+      <c r="J2335">
+        <v>360000</v>
+      </c>
+      <c r="K2335" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2335" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2336" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2336">
+        <v>1064</v>
+      </c>
+      <c r="B2336" t="s">
+        <v>217</v>
+      </c>
+      <c r="C2336" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2336" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2336" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2336" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2336" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2336">
+        <v>27</v>
+      </c>
+      <c r="I2336">
+        <v>30000</v>
+      </c>
+      <c r="J2336">
+        <v>810000</v>
+      </c>
+      <c r="K2336" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2336" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2337" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2337">
+        <v>752</v>
+      </c>
+      <c r="B2337" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2337" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2337" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2337" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2337" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2337" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2337">
+        <v>15</v>
+      </c>
+      <c r="I2337">
+        <v>30000</v>
+      </c>
+      <c r="J2337">
+        <v>450031</v>
+      </c>
+      <c r="K2337" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2337" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2338" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2338">
+        <v>696</v>
+      </c>
+      <c r="B2338" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2338" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2338" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2338" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2338" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2338" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2338">
+        <v>14</v>
+      </c>
+      <c r="I2338">
+        <v>792</v>
+      </c>
+      <c r="J2338">
+        <v>11214</v>
+      </c>
+      <c r="K2338" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2338" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2339" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2339">
+        <v>1835</v>
+      </c>
+      <c r="B2339" t="s">
+        <v>349</v>
+      </c>
+      <c r="C2339" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2339" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2339" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2339" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2339" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2339">
+        <v>18</v>
+      </c>
+      <c r="I2339">
+        <v>3507</v>
+      </c>
+      <c r="J2339">
+        <v>63000</v>
+      </c>
+      <c r="K2339" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2339" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2340" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2340">
+        <v>1936</v>
+      </c>
+      <c r="B2340" t="s">
+        <v>362</v>
+      </c>
+      <c r="C2340" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2340" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2340" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2340" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2340" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2340">
+        <v>31</v>
+      </c>
+      <c r="I2340">
+        <v>60</v>
+      </c>
+      <c r="J2340">
+        <v>1860</v>
+      </c>
+      <c r="K2340" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2340" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2341" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2341">
+        <v>298</v>
+      </c>
+      <c r="B2341" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2341" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2341" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2341" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2341" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2341" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2341">
+        <v>8</v>
+      </c>
+      <c r="I2341">
+        <v>18</v>
+      </c>
+      <c r="J2341">
+        <v>505</v>
+      </c>
+      <c r="K2341" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2341" t="s">
         <v>18</v>
       </c>
     </row>
